--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486561_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486561_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>C. JÜRGENS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3327</v>
+        <v>3.5276</v>
       </c>
       <c r="E2" t="n">
-        <v>5.113</v>
+        <v>2.4452</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7804</v>
+        <v>1.0824</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2724</v>
+        <v>4.1916</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3664</v>
+        <v>2.2385</v>
       </c>
       <c r="I2" t="n">
-        <v>0.906</v>
+        <v>1.9531</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6981</v>
+        <v>2.9844</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8167</v>
+        <v>2.3724</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8813</v>
+        <v>0.612</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4257</v>
+        <v>1.2072</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4504</v>
+        <v>-0.1339</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0247</v>
+        <v>1.3411</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1478</v>
+        <v>-0.0342</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3073</v>
+        <v>-0.1694</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1595</v>
+        <v>0.1352</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-1.4997</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1952</v>
+        <v>-0.3698</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. JÜRGENS</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7723</v>
+        <v>2.8605</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9982</v>
+        <v>3.5484</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7742</v>
+        <v>-0.6879</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1916</v>
+        <v>3.2724</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2385</v>
+        <v>2.3664</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9531</v>
+        <v>0.906</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9844</v>
+        <v>3.6981</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3724</v>
+        <v>2.8167</v>
       </c>
       <c r="L3" t="n">
-        <v>0.612</v>
+        <v>0.8813</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2072</v>
+        <v>-0.4257</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1339</v>
+        <v>-0.4504</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3411</v>
+        <v>0.0247</v>
       </c>
       <c r="P3" t="n">
-        <v>0.87</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7895</v>
+        <v>0.6757</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6165</v>
+        <v>0.7427</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.173</v>
+        <v>-0.067</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4997</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3698</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0089</v>
+        <v>1.7199</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.642</v>
+        <v>-0.5303</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6509</v>
+        <v>2.2502</v>
       </c>
       <c r="G4" t="n">
         <v>0.7451</v>
@@ -766,13 +766,13 @@
         <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8288</v>
+        <v>0.5399</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.262</v>
+        <v>-0.1502</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0908</v>
+        <v>0.6901</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3685</v>
+        <v>0.9522</v>
       </c>
       <c r="E5" t="n">
-        <v>1.949</v>
+        <v>1.502</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5806</v>
+        <v>-0.5497</v>
       </c>
       <c r="G5" t="n">
         <v>0.8666</v>
@@ -844,13 +844,13 @@
         <v>0.2175</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4796</v>
+        <v>0.0634</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1971</v>
+        <v>-0.2499</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2825</v>
+        <v>0.3133</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0481</v>
+        <v>0.8227</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4135</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3653</v>
+        <v>-0.1496</v>
       </c>
       <c r="G6" t="n">
         <v>1.8478</v>
@@ -922,13 +922,13 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6697</v>
+        <v>0.1048</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8099</v>
+        <v>-0.2511</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1402</v>
+        <v>0.356</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1966</v>
+        <v>-0.2351</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1062</v>
+        <v>-0.3298</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.09030000000000001</v>
+        <v>0.0946</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5152</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5138</v>
+        <v>0.4753</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4711</v>
+        <v>0.2476</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0428</v>
+        <v>0.2277</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1952</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0935</v>
+        <v>-0.2611</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6457000000000001</v>
+        <v>0.2484</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4478</v>
+        <v>-0.5094</v>
       </c>
       <c r="G8" t="n">
         <v>0.5569</v>
@@ -1078,13 +1078,13 @@
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2382</v>
+        <v>0.5942</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9469</v>
+        <v>-0.0529</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7087</v>
+        <v>0.6471</v>
       </c>
       <c r="V8" t="n">
         <v>-2.0647</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. SARAIVA SEIXAS</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1634</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4932</v>
+        <v>0.8943</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6702</v>
+        <v>-1.416</v>
       </c>
       <c r="G9" t="n">
-        <v>0.395</v>
+        <v>2.7302</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7031</v>
+        <v>2.6369</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0981</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9028</v>
+        <v>3.2403</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7236</v>
+        <v>3.0873</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6264</v>
+        <v>0.153</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5077</v>
+        <v>-0.5101</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9794</v>
+        <v>-0.4504</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4717</v>
+        <v>-0.0598</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5225</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0359</v>
+        <v>-0.2073</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3509</v>
+        <v>0.0036</v>
       </c>
       <c r="U9" t="n">
-        <v>0.315</v>
+        <v>-0.2109</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.3045</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>-0.1745</v>
       </c>
       <c r="X9" t="n">
         <v>-1.13</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>D. SARAIVA SEIXAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2308</v>
+        <v>-1.3561</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002</v>
+        <v>-0.7167</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2311</v>
+        <v>-0.6394</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7302</v>
+        <v>0.395</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6369</v>
+        <v>-1.7031</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09320000000000001</v>
+        <v>2.0981</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2403</v>
+        <v>0.9028</v>
       </c>
       <c r="K10" t="n">
-        <v>3.0873</v>
+        <v>-0.7236</v>
       </c>
       <c r="L10" t="n">
-        <v>0.153</v>
+        <v>1.6264</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5101</v>
+        <v>-0.5077</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4504</v>
+        <v>-0.9794</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0598</v>
+        <v>0.4717</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7401</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9164</v>
+        <v>-0.2286</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8904</v>
+        <v>-0.5744</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.026</v>
+        <v>0.3458</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3045</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1745</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1326</v>
+        <v>-3.0517</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5731</v>
+        <v>-2.4614</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5595</v>
+        <v>-0.5903</v>
       </c>
       <c r="G11" t="n">
         <v>-2.814</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5361</v>
+        <v>-0.4551</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1251</v>
+        <v>-0.1559</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0066</v>
+        <v>-4.7598</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.311</v>
+        <v>-5.3628</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6956</v>
+        <v>0.603</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9552</v>
+        <v>-4.6309</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9701</v>
+        <v>-2.9256</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9253</v>
+        <v>-1.7053</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5286</v>
+        <v>-4.7391</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1894</v>
+        <v>-2.5422</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.718</v>
+        <v>-2.1969</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4266</v>
+        <v>0.1083</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2193</v>
+        <v>-0.3834</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2073</v>
+        <v>0.4916</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.8276</v>
+        <v>0.435</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5157</v>
+        <v>-0.5639</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2197</v>
+        <v>-0.6237</v>
       </c>
       <c r="U12" t="n">
-        <v>0.296</v>
+        <v>0.0598</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1259</v>
+        <v>-5.1164</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6981</v>
+        <v>-4.2051</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5722</v>
+        <v>-0.9114</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.6309</v>
+        <v>-1.9552</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.9256</v>
+        <v>0.9701</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7053</v>
+        <v>-2.9253</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.7391</v>
+        <v>-0.5286</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.5422</v>
+        <v>1.1894</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.1969</v>
+        <v>-1.718</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1083</v>
+        <v>-1.4266</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3834</v>
+        <v>-0.2193</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4916</v>
+        <v>-1.2073</v>
       </c>
       <c r="P13" t="n">
-        <v>0.435</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R13" t="n">
         <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.93</v>
+        <v>0.4059</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9589</v>
+        <v>0.3257</v>
       </c>
       <c r="U13" t="n">
-        <v>0.029</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.4189</v>
+        <v>-5.419</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.995399999999999</v>
+        <v>-3.995499999999998</v>
       </c>
       <c r="F14" t="n">
         <v>-1.4235</v>
       </c>
       <c r="G14" t="n">
-        <v>4.690300000000003</v>
+        <v>4.690300000000001</v>
       </c>
       <c r="H14" t="n">
         <v>10.2046</v>
@@ -1546,10 +1546,10 @@
         <v>5.437499999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>1.369900000000001</v>
+        <v>1.3701</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0513</v>
+        <v>-1.0512</v>
       </c>
       <c r="U14" t="n">
         <v>2.4214</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>M. TOWNES VILLAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3208</v>
+        <v>3.9882</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1914</v>
+        <v>3.4311</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1294</v>
+        <v>0.5571</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7005</v>
+        <v>2.8835</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9977</v>
+        <v>-1.3805</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6981</v>
+        <v>4.264</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8911</v>
+        <v>3.3571</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5141</v>
+        <v>0.5633</v>
       </c>
       <c r="L15" t="n">
-        <v>1.377</v>
+        <v>2.7938</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1907</v>
+        <v>-0.4736</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5118</v>
+        <v>-1.9438</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3212</v>
+        <v>1.4702</v>
       </c>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>-1.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8155</v>
+        <v>-0.2406</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1703</v>
+        <v>-0.4014</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3548</v>
+        <v>0.1607</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9347</v>
+        <v>2.6504</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>2.6504</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. TOWNES VILLAR</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5335</v>
+        <v>3.8063</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7606</v>
+        <v>3.7385</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7729</v>
+        <v>0.0677</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8835</v>
+        <v>1.7005</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3805</v>
+        <v>-0.9977</v>
       </c>
       <c r="I16" t="n">
-        <v>4.264</v>
+        <v>2.6981</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3571</v>
+        <v>1.8911</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5633</v>
+        <v>0.5141</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7938</v>
+        <v>1.377</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4736</v>
+        <v>-0.1907</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9438</v>
+        <v>-1.5118</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4702</v>
+        <v>1.3212</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6954</v>
+        <v>0.301</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0719</v>
+        <v>0.7174</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3765</v>
+        <v>-0.4164</v>
       </c>
       <c r="V16" t="n">
-        <v>2.6504</v>
+        <v>0.9347</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6504</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6821</v>
+        <v>1.8909</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8145</v>
+        <v>0.3675</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8676</v>
+        <v>1.5235</v>
       </c>
       <c r="G17" t="n">
         <v>1.0056</v>
@@ -1780,13 +1780,13 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3067</v>
+        <v>0.5155</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1214</v>
+        <v>-0.5684</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4281</v>
+        <v>1.0839</v>
       </c>
       <c r="V17" t="n">
         <v>0.3698</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6119</v>
+        <v>0.662</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5154</v>
+        <v>0.6272</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0965</v>
+        <v>0.0348</v>
       </c>
       <c r="G18" t="n">
         <v>-1.025</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2449</v>
+        <v>0.295</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0565</v>
+        <v>0.0553</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3014</v>
+        <v>0.2397</v>
       </c>
       <c r="V18" t="n">
         <v>0.7395</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4372</v>
+        <v>0.2128</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7655</v>
+        <v>-0.5419</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3283</v>
+        <v>0.7547</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2199</v>
@@ -1936,13 +1936,13 @@
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.2851</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3148</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6202</v>
+        <v>-0.1938</v>
       </c>
       <c r="V19" t="n">
         <v>0.1952</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7457</v>
+        <v>0.1508</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4151</v>
+        <v>-2.1916</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6694</v>
+        <v>2.3424</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0899</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1131</v>
+        <v>-0.2166</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0154</v>
+        <v>-0.7919</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0977</v>
+        <v>0.5753</v>
       </c>
       <c r="V20" t="n">
         <v>0.3698</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9595</v>
+        <v>-0.4312</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3343</v>
+        <v>-0.4721</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3748</v>
+        <v>0.0409</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7176</v>
+        <v>-3.3981</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0889</v>
+        <v>-1.7367</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6287</v>
+        <v>-1.6614</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2808</v>
+        <v>-2.362</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6721</v>
+        <v>0.0246</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6088</v>
+        <v>-2.3865</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4368</v>
+        <v>-1.0362</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4169</v>
+        <v>-1.7613</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0199</v>
+        <v>0.7251</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5018</v>
+        <v>-0.4029</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6609</v>
+        <v>-0.3701</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1591</v>
+        <v>-0.0328</v>
       </c>
       <c r="V21" t="n">
-        <v>1.695</v>
+        <v>2.0647</v>
       </c>
       <c r="W21" t="n">
-        <v>1.695</v>
+        <v>2.2599</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1468</v>
+        <v>-0.7719</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2544</v>
+        <v>-1.1108</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1076</v>
+        <v>0.3389</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3981</v>
+        <v>-1.7176</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7367</v>
+        <v>-1.0889</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6614</v>
+        <v>-0.6287</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.362</v>
+        <v>-1.2808</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0246</v>
+        <v>-0.6721</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.3865</v>
+        <v>-0.6088</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0362</v>
+        <v>-0.4368</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7613</v>
+        <v>-0.4169</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7251</v>
+        <v>-0.0199</v>
       </c>
       <c r="P22" t="n">
-        <v>1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1184</v>
+        <v>-0.3142</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1524</v>
+        <v>-0.4374</v>
       </c>
       <c r="U22" t="n">
-        <v>0.034</v>
+        <v>0.1232</v>
       </c>
       <c r="V22" t="n">
-        <v>2.0647</v>
+        <v>1.695</v>
       </c>
       <c r="W22" t="n">
-        <v>2.2599</v>
+        <v>1.695</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5486</v>
+        <v>-1.2519</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7703</v>
+        <v>-1.6586</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2217</v>
+        <v>0.4067</v>
       </c>
       <c r="G23" t="n">
         <v>0.0953</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4487</v>
+        <v>-0.152</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1678</v>
+        <v>0.3527</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7602</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8915</v>
+        <v>-2.092</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3188</v>
+        <v>-0.7658</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5728</v>
+        <v>-1.3262</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9246</v>
@@ -2326,13 +2326,13 @@
         <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0755</v>
+        <v>-0.125</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4182</v>
+        <v>-0.0288</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3427</v>
+        <v>-0.0961</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.419000000000001</v>
+        <v>6.164</v>
       </c>
       <c r="E25" t="n">
         <v>1.423500000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>3.995400000000001</v>
+        <v>4.7405</v>
       </c>
       <c r="G25" t="n">
         <v>-4.690200000000001</v>
@@ -2404,13 +2404,13 @@
         <v>9.7875</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3698</v>
+        <v>-0.6248999999999999</v>
       </c>
       <c r="T25" t="n">
         <v>-2.4213</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0515</v>
+        <v>1.7964</v>
       </c>
       <c r="V25" t="n">
         <v>7.128900000000002</v>
